--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486353_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486353_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4728</v>
+        <v>5.8756</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1024</v>
+        <v>6.3512</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6296</v>
+        <v>-0.4755</v>
       </c>
       <c r="G2" t="n">
         <v>6.2706</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7108</v>
+        <v>-0.3079</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4242</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0379</v>
+        <v>0.1163</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7395</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6591</v>
+        <v>4.7691</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5858</v>
+        <v>6.3875</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9267</v>
+        <v>-1.6184</v>
       </c>
       <c r="G3" t="n">
         <v>5.5051</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2415</v>
+        <v>0.3515</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2896</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0481</v>
+        <v>0.2602</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.756</v>
+        <v>2.0857</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7743</v>
+        <v>3.1348</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0183</v>
+        <v>-1.0491</v>
       </c>
       <c r="G4" t="n">
         <v>1.2971</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4111</v>
+        <v>-0.0814</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5239</v>
+        <v>-0.1634</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1128</v>
+        <v>0.082</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.452</v>
+        <v>1.64</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1048</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3472</v>
+        <v>1.1315</v>
       </c>
       <c r="G5" t="n">
         <v>0.091</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2311</v>
+        <v>0.4191</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3425</v>
+        <v>0.0613</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5736</v>
+        <v>0.3578</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1692</v>
+        <v>0.8803</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.672</v>
+        <v>-0.5603</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8412</v>
+        <v>1.4405</v>
       </c>
       <c r="G6" t="n">
         <v>0.8216</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.2539</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9538</v>
+        <v>0.5531</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1952</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.729</v>
+        <v>0.6767</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1028</v>
+        <v>0.2397</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6263</v>
+        <v>0.4369</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3098</v>
+        <v>-0.154</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8457</v>
+        <v>-0.146</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1555</v>
+        <v>-0.008</v>
       </c>
       <c r="J7" t="n">
-        <v>0.949</v>
+        <v>0.113</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5443</v>
+        <v>0.0365</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4933</v>
+        <v>0.0765</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6392</v>
+        <v>-0.267</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3013</v>
+        <v>-0.1825</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3379</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4866</v>
+        <v>-0.0171</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0911</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3955</v>
+        <v>0.0514</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6458</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2397</v>
+        <v>-0.7228</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4061</v>
+        <v>0.6571</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.154</v>
+        <v>0.3098</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.146</v>
+        <v>-0.8457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.008</v>
+        <v>1.1555</v>
       </c>
       <c r="J8" t="n">
-        <v>0.113</v>
+        <v>0.949</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0365</v>
+        <v>-0.5443</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0765</v>
+        <v>1.4933</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.267</v>
+        <v>-0.6392</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1825</v>
+        <v>-0.3013</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.3379</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0479</v>
+        <v>0.6919</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.2656</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0205</v>
+        <v>0.4263</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2542</v>
+        <v>-1.7654</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0459</v>
+        <v>-0.0639</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2083</v>
+        <v>-1.7015</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5553</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6061</v>
+        <v>0.0949</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0649</v>
+        <v>-0.0829</v>
       </c>
       <c r="U9" t="n">
-        <v>0.671</v>
+        <v>0.1778</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4404</v>
+        <v>-1.9018</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.563</v>
+        <v>-1.271</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8774</v>
+        <v>-0.6308</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0328</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0601</v>
+        <v>-0.5215</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.3245</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4437</v>
+        <v>-0.1971</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7267</v>
+        <v>-3.1572</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6739</v>
+        <v>-2.3818</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0528</v>
+        <v>-0.7754</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5382</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5805</v>
+        <v>-0.0111</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.536</v>
+        <v>-0.2439</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0446</v>
+        <v>0.2328</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9554</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.995</v>
+        <v>-4.542</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6359</v>
+        <v>-2.2754</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3591</v>
+        <v>-2.2666</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5645</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8204</v>
+        <v>-0.3674</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5239</v>
+        <v>-0.1634</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2965</v>
+        <v>-0.204</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.467599999999998</v>
+        <v>4.4953</v>
       </c>
       <c r="E13" t="n">
-        <v>8.319099999999999</v>
+        <v>9.346600000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.8514</v>
+        <v>-4.8513</v>
       </c>
       <c r="G13" t="n">
         <v>6.450400000000001</v>
@@ -1468,13 +1468,13 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5226999999999999</v>
+        <v>0.5049000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3794</v>
+        <v>-1.3518</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8564</v>
+        <v>1.8566</v>
       </c>
       <c r="V13" t="n">
         <v>1.890299999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.734</v>
+        <v>4.9226</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5869</v>
+        <v>4.1144</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1471</v>
+        <v>0.8082</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3891</v>
+        <v>0.1127</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0373</v>
+        <v>-1.8157</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4265</v>
+        <v>1.9284</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8573</v>
+        <v>3.2278</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8395</v>
+        <v>-0.1214</v>
       </c>
       <c r="L14" t="n">
-        <v>4.0178</v>
+        <v>3.3492</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4681</v>
+        <v>-3.1151</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8768</v>
+        <v>-1.6943</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5913</v>
+        <v>-1.4208</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5173</v>
+        <v>0.0219</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2704</v>
+        <v>-0.4386</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7876</v>
+        <v>0.4605</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.13</v>
+        <v>2.3954</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.13</v>
+        <v>1.0702</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0408</v>
+        <v>4.8244</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8833</v>
+        <v>6.5539</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8425</v>
+        <v>-1.7295</v>
       </c>
       <c r="G15" t="n">
         <v>3.7459</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2963</v>
+        <v>0.4873</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0154</v>
+        <v>-0.3449</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7191</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0.1562</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7755</v>
+        <v>4.404</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3321</v>
+        <v>4.6987</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4434</v>
+        <v>-0.2946</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1127</v>
+        <v>2.3891</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8157</v>
+        <v>-1.0373</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9284</v>
+        <v>3.4265</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2278</v>
+        <v>4.8573</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1214</v>
+        <v>0.8395</v>
       </c>
       <c r="L16" t="n">
-        <v>3.3492</v>
+        <v>4.0178</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1151</v>
+        <v>-2.4681</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6943</v>
+        <v>-1.8768</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4208</v>
+        <v>-0.5913</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1251</v>
+        <v>1.1873</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2209</v>
+        <v>-0.1586</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0958</v>
+        <v>1.3459</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3954</v>
+        <v>-1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.0702</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2752</v>
+        <v>0.394</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6587</v>
+        <v>-0.3234</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3835</v>
+        <v>0.7174</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9945000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8032</v>
+        <v>-0.134</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1867</v>
+        <v>0.1472</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9987</v>
+        <v>-1.2528</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.443</v>
+        <v>-0.8255</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5557</v>
+        <v>-0.4272</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8709</v>
+        <v>-1.436</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2222</v>
+        <v>-1.0918</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6487</v>
+        <v>-0.3442</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0449</v>
+        <v>-0.6886</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6752</v>
+        <v>-0.7268</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6303</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9158</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8974</v>
+        <v>-0.365</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0184</v>
+        <v>-0.3825</v>
       </c>
       <c r="P18" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6937</v>
+        <v>-0.0342</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5997</v>
+        <v>-0.137</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0941</v>
+        <v>0.1027</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.039</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3144</v>
+        <v>-1.3715</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8255</v>
+        <v>-0.2115</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4889</v>
+        <v>-1.1601</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.436</v>
+        <v>-1.1349</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0918</v>
+        <v>-0.0639</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3442</v>
+        <v>-1.071</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6886</v>
+        <v>0.113</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7268</v>
+        <v>0.0365</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>0.0765</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-1.2479</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.365</v>
+        <v>-0.1004</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3825</v>
+        <v>-1.1475</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0959</v>
+        <v>-0.5026</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.137</v>
+        <v>-0.3245</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0411</v>
+        <v>-0.1782</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.604</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.604</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6259</v>
+        <v>-1.5395</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.435</v>
+        <v>-1.2253</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1909</v>
+        <v>-0.3142</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1349</v>
+        <v>-1.8709</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0639</v>
+        <v>-0.2222</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.071</v>
+        <v>-1.6487</v>
       </c>
       <c r="J20" t="n">
-        <v>0.113</v>
+        <v>0.0449</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0365</v>
+        <v>0.6752</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0765</v>
+        <v>-0.6303</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2479</v>
+        <v>-1.9158</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1004</v>
+        <v>-0.8974</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1475</v>
+        <v>-1.0184</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7569</v>
+        <v>0.1529</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.548</v>
+        <v>-0.1826</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.209</v>
+        <v>0.3356</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.604</v>
+        <v>-0.039</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.604</v>
+        <v>-0.039</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5099</v>
+        <v>-2.9261</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2601</v>
+        <v>-0.7071</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2499</v>
+        <v>-2.219</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6596</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0566</v>
+        <v>-0.3596</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3341</v>
+        <v>-0.113</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2775</v>
+        <v>-0.2466</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5595</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4323</v>
+        <v>-4.0984</v>
       </c>
       <c r="E22" t="n">
         <v>-2.1659</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2664</v>
+        <v>-1.9324</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0366</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2636</v>
+        <v>0.0703</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2019</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0618</v>
+        <v>0.2722</v>
       </c>
       <c r="V22" t="n">
         <v>0.3904</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8617</v>
+        <v>-5.3345</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1628</v>
+        <v>-5.0568</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6989</v>
+        <v>-0.2776</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5657</v>
@@ -2248,13 +2248,13 @@
         <v>1.9576</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5963</v>
+        <v>1.1236</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2197</v>
+        <v>0.3257</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3766</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4997</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.467800000000001</v>
+        <v>-1.9778</v>
       </c>
       <c r="E24" t="n">
-        <v>4.851299999999999</v>
+        <v>4.851499999999997</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.3192</v>
+        <v>-6.828999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-6.4505</v>
@@ -2302,7 +2302,7 @@
         <v>12.1297</v>
       </c>
       <c r="K24" t="n">
-        <v>3.0135</v>
+        <v>3.013499999999999</v>
       </c>
       <c r="L24" t="n">
         <v>9.116100000000001</v>
@@ -2326,13 +2326,13 @@
         <v>14.1379</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5228999999999999</v>
+        <v>2.0129</v>
       </c>
       <c r="T24" t="n">
         <v>-1.8566</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3793</v>
+        <v>3.869400000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8902</v>
